--- a/files/08-1811-s-bentley-ave.xlsx
+++ b/files/08-1811-s-bentley-ave.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2B03492-2A0B-4036-AC6F-DE79FC74068B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43BAACF-6CB3-4D36-B6BE-4DB8966A65BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EAE0DFCE-2F93-4F9A-8760-3BAF0CA1B52B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{390B8E41-5716-4EE3-9120-50D818E7815C}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
     <sheet name="08 1811 S Bentley Ave" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'08 1811 S Bentley Ave'!$A$1:$N$78</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -195,7 +192,10 @@
     <t>LoopNet listing</t>
   </si>
   <si>
-    <t>Data pulled 9/17/2026 from LoopNet public listing</t>
+    <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Lyon Stahl / Serhant / Taksa, rent roll 9/1/2026)</t>
+  </si>
+  <si>
+    <t>NOTE: | OM: Rent roll cross-check OK: 15 unit rents sum to $47,128/mo vs OM $47,127 (rounding); x12 = $565,536 vs OM $565,525 annual (0.002%).; Expense line items sum to $188,808, not the OM's stated total of $191,916 (short $3,108, 1.6%). NOI of $359,435 is computed off the $191,916 total; recomputed on the li | OM: Rent roll cross-check OK: 15 unit rents sum to $47,128/mo vs OM $47,127 (rounding); x12 = $565,536 vs OM $565,525 annual (0.002%).; Expense line items sum to $188,808, not the OM's stated total of $191,916 (short $3,108, 1.6%). NOI of $359,435 is computed off the $191,916 total; recomputed on the li</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -300,19 +300,19 @@
     <t>Rent source</t>
   </si>
   <si>
-    <t>1 Bd / 1 Ba  (~550 SF)</t>
-  </si>
-  <si>
-    <t>Allocated from published GRM (price / GRM) using LAAA bed weights</t>
-  </si>
-  <si>
-    <t>2 Bd / 1 Ba  (~800 SF)</t>
-  </si>
-  <si>
-    <t>2 Bd / 2 Ba  (~800 SF)</t>
-  </si>
-  <si>
-    <t>3 Bd / 2 Ba  (~1100 SF)</t>
+    <t>1 Bd / 1 Ba  [Unit 304, Non-RSO; at market ($2,900)]</t>
+  </si>
+  <si>
+    <t>OM rent roll, current in-place rents (OM rent roll 9/1/2026)</t>
+  </si>
+  <si>
+    <t>2 Bd / 1 Ba  [Unit 204, RSO; market $3,100]</t>
+  </si>
+  <si>
+    <t>2 Bd / 2 Ba  [Units 100,101,102,103,200,203,303; rents $2,131 to $3,345 (s]</t>
+  </si>
+  <si>
+    <t>3 Bd / 2 Ba  [Units 201,202,205,301,302,305; rents $3,531 to $3,952 (sum $]</t>
   </si>
   <si>
     <t>Total / weighted avg</t>
@@ -333,7 +333,7 @@
     <t>Scheduled gross rent</t>
   </si>
   <si>
-    <t>OM column: price / published GRM</t>
+    <t>OM column: OM stated current scheduled rent (OM rent roll 9/1/2026); LAAA column: OM rent roll by unit type</t>
   </si>
   <si>
     <t>Other income (laundry, parking, RUBS)</t>
@@ -345,7 +345,7 @@
     <t>Vacancy &amp; credit loss</t>
   </si>
   <si>
-    <t>OM 3.0% (OM figure if extracted, else 3% assumed); LAAA per Assumptions</t>
+    <t>OM 3.0%; LAAA per Assumptions</t>
   </si>
   <si>
     <t>Effective gross income</t>
@@ -390,7 +390,7 @@
     <t>Utilities (water/sewer/trash/common electric &amp; gas)</t>
   </si>
   <si>
-    <t>per unit, by city</t>
+    <t>per unit, by city; OM utilities + water/sewer + gas/electric + trash combined</t>
   </si>
   <si>
     <t>Contract services (landscape, pest, cleaning)</t>
@@ -399,10 +399,10 @@
     <t>per unit</t>
   </si>
   <si>
-    <t>Admin / legal / licenses / rent registration</t>
-  </si>
-  <si>
-    <t>per unit; OM "other" items land here</t>
+    <t>Admin / legal / licenses / rent registration / other OM items</t>
+  </si>
+  <si>
+    <t>OM other items: Direct Assessments (2026 actual) 2,554; Maintenance Supplies (2026 annualized) 2,935; Utilities - Telephone (2026 annualized) 767; Elevator (2026 annualized) 2,724; Cleaning &amp; Other Se</t>
   </si>
   <si>
     <t>Replacement reserves</t>
@@ -411,7 +411,7 @@
     <t>Total operating expenses</t>
   </si>
   <si>
-    <t>OM line items not published. OM total IMPLIED = OM EGI - (price x published cap)</t>
+    <t>OM line items from OM (OM rent roll 9/1/2026); basis: OM 'Current' column of the Pro Forma Annual Operating Expenses page. Mixed basis: taxes projected at 1.187% x sale price, management 4.0% x GOI (projected), insurance $1.18/GSF (labeled actual), R&amp;M $1,500/unit and reserves $350/unit projected; direct assessments and all utility/service lines are 2026 actual/annualized. gas_electric is gas only (no electric line). utilities key left null because the OM breaks utilities out by line.; OM total 191,916</t>
   </si>
   <si>
     <t>Expenses per unit</t>
@@ -427,6 +427,9 @@
   </si>
   <si>
     <t>Net operating income</t>
+  </si>
+  <si>
+    <t>OM states NOI 359,435 / cap 5.66</t>
   </si>
   <si>
     <t>Cap rate on asking price</t>
@@ -475,12 +478,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,9 +529,24 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -565,7 +584,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -601,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -614,6 +634,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -621,16 +642,18 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,7 +686,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39671504-1702-4A86-9A8F-8D21671075E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D03B9B2-6CEF-41F3-B3C2-2295EDAC5A09}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,7 +997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5DC949F-7A22-44E9-B8C1-76BE799C23C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2298BD12-A3E1-49DB-B66B-7A09864FB10A}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1343,7 +1366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442CDC51-DA06-45FA-86BD-D26F6F43706D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7D02FB-B627-4F17-99CE-137E7BBE5DFB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1374,85 +1397,90 @@
         <v>50</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="14">
+        <v>53</v>
+      </c>
+      <c r="B7" s="15">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="14">
+        <v>54</v>
+      </c>
+      <c r="B8" s="15">
         <v>16568</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="14">
+        <v>55</v>
+      </c>
+      <c r="B9" s="15">
         <v>11761</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="15">
+        <v>56</v>
+      </c>
+      <c r="B10" s="16">
         <v>0.27</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="8">
         <v>5866611</v>
@@ -1460,38 +1488,38 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="4">
         <v>6350000</v>
@@ -1499,7 +1527,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="8">
         <f>IFERROR(B22/B7,"")</f>
@@ -1508,617 +1536,636 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="16">
+        <v>76</v>
+      </c>
+      <c r="B24" s="17">
         <f>IFERROR(B22/B8,"")</f>
         <v>383.26895219700629</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="17">
+        <v>77</v>
+      </c>
+      <c r="B25" s="18">
         <v>5.6599999999999998E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="18">
+        <v>78</v>
+      </c>
+      <c r="B26" s="19">
         <v>11.23</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+      <c r="A28" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="19" t="s">
+      <c r="A29" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="D29" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="E29" s="20" t="s">
         <v>84</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="14">
-        <v>2</v>
-      </c>
-      <c r="C30" s="20">
-        <v>2147</v>
-      </c>
-      <c r="D30" s="8">
+        <v>86</v>
+      </c>
+      <c r="B30" s="15">
+        <v>1</v>
+      </c>
+      <c r="C30" s="21">
+        <v>2900</v>
+      </c>
+      <c r="D30" s="22">
         <f>B30*C30</f>
-        <v>4294</v>
-      </c>
-      <c r="E30" s="8">
+        <v>2900</v>
+      </c>
+      <c r="E30" s="22">
         <f>D30*12</f>
-        <v>51528</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>86</v>
+        <v>34800</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="15">
+        <v>1</v>
+      </c>
+      <c r="C31" s="21">
+        <v>2648</v>
+      </c>
+      <c r="D31" s="22">
+        <f>B31*C31</f>
+        <v>2648</v>
+      </c>
+      <c r="E31" s="22">
+        <f>D31*12</f>
+        <v>31776</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>87</v>
-      </c>
-      <c r="B31" s="14">
-        <v>1</v>
-      </c>
-      <c r="C31" s="20">
-        <v>2898</v>
-      </c>
-      <c r="D31" s="8">
-        <f>B31*C31</f>
-        <v>2898</v>
-      </c>
-      <c r="E31" s="8">
-        <f>D31*12</f>
-        <v>34776</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="14">
-        <v>6</v>
-      </c>
-      <c r="C32" s="20">
-        <v>2898</v>
-      </c>
-      <c r="D32" s="8">
+        <v>89</v>
+      </c>
+      <c r="B32" s="15">
+        <v>7</v>
+      </c>
+      <c r="C32" s="21">
+        <v>2699</v>
+      </c>
+      <c r="D32" s="22">
         <f>B32*C32</f>
-        <v>17388</v>
-      </c>
-      <c r="E32" s="8">
+        <v>18893</v>
+      </c>
+      <c r="E32" s="22">
         <f>D32*12</f>
-        <v>208656</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>86</v>
+        <v>226716</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="14">
+        <v>90</v>
+      </c>
+      <c r="B33" s="15">
         <v>6</v>
       </c>
-      <c r="C33" s="20">
-        <v>3757</v>
-      </c>
-      <c r="D33" s="8">
+      <c r="C33" s="21">
+        <v>3780</v>
+      </c>
+      <c r="D33" s="22">
         <f>B33*C33</f>
-        <v>22542</v>
-      </c>
-      <c r="E33" s="8">
+        <v>22680</v>
+      </c>
+      <c r="E33" s="22">
         <f>D33*12</f>
-        <v>270504</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>86</v>
+        <v>272160</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="22">
+      <c r="A34" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="25">
         <f>SUM(B30:B33)</f>
         <v>15</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="26">
         <f>IFERROR(D34/B34,"")</f>
-        <v>3141.4666666666667</v>
-      </c>
-      <c r="D34" s="23">
+        <v>3141.4</v>
+      </c>
+      <c r="D34" s="26">
         <f>SUM(D30:D33)</f>
-        <v>47122</v>
-      </c>
-      <c r="E34" s="23">
+        <v>47121</v>
+      </c>
+      <c r="E34" s="26">
         <f>SUM(E30:E33)</f>
-        <v>565464</v>
+        <v>565452</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="A36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="24" t="s">
+      <c r="A37" s="27"/>
+      <c r="B37" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24" t="s">
+      <c r="C37" s="27" t="s">
         <v>94</v>
+      </c>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="8">
-        <v>565449.68833481742</v>
+        <v>96</v>
+      </c>
+      <c r="B38" s="22">
+        <v>565525</v>
       </c>
       <c r="C38" s="8">
         <f>E34</f>
-        <v>565464</v>
+        <v>565452</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B39" s="8">
-        <v>0</v>
+        <v>2791</v>
       </c>
       <c r="C39" s="4">
-        <v>0</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>98</v>
+      <c r="A40" s="24" t="s">
+        <v>99</v>
       </c>
       <c r="B40" s="8">
         <f>B38+B39</f>
-        <v>565449.68833481742</v>
+        <v>568316</v>
       </c>
       <c r="C40" s="8">
         <f>C38+C39</f>
-        <v>565464</v>
+        <v>568243</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B41" s="8">
         <f>-B38*0.03</f>
-        <v>-16963.490650044521</v>
+        <v>-16965.75</v>
       </c>
       <c r="C41" s="8">
         <f>-C38*Assumptions!$B$3</f>
-        <v>-16963.919999999998</v>
+        <v>-16963.559999999998</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="23">
+      <c r="A42" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="26">
         <f>B40+B41</f>
-        <v>548486.19768477289</v>
-      </c>
-      <c r="C42" s="23">
+        <v>551350.25</v>
+      </c>
+      <c r="C42" s="26">
         <f>C40+C41</f>
-        <v>548500.07999999996</v>
+        <v>551279.43999999994</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
+      <c r="A44" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="24" t="s">
+      <c r="A45" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="24" t="s">
+      <c r="B45" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="C45" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F45" s="24" t="s">
+      <c r="D45" s="27" t="s">
         <v>94</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="B46" s="22">
+        <v>75399</v>
+      </c>
       <c r="C46" s="8">
         <f>B22*Assumptions!$B$15</f>
         <v>79375</v>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="28">
         <f>C46</f>
         <v>79375</v>
       </c>
-      <c r="E46" s="8" t="str">
+      <c r="E46" s="8">
         <f t="shared" ref="E46:E54" si="0">IF(ISNUMBER(B46),D46-B46,"")</f>
-        <v/>
+        <v>3976</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="B47" s="22">
+        <v>19527</v>
+      </c>
       <c r="C47" s="8">
         <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
         <v>19568</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="28">
         <f t="shared" ref="D47:D53" si="1">IF(ISNUMBER(B47),MAX(B47,C47),C47)</f>
         <v>19568</v>
       </c>
-      <c r="E47" s="8" t="str">
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>41</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="8"/>
+        <v>111</v>
+      </c>
+      <c r="B48" s="22">
+        <v>22054</v>
+      </c>
       <c r="C48" s="8">
         <f>C42*Assumptions!$B$4</f>
-        <v>27425.004000000001</v>
-      </c>
-      <c r="D48" s="25">
+        <v>27563.971999999998</v>
+      </c>
+      <c r="D48" s="28">
         <f t="shared" si="1"/>
-        <v>27425.004000000001</v>
-      </c>
-      <c r="E48" s="8" t="str">
+        <v>27563.971999999998</v>
+      </c>
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5509.9719999999979</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="8"/>
+        <v>113</v>
+      </c>
+      <c r="B49" s="22">
+        <v>22500</v>
+      </c>
       <c r="C49" s="8">
         <f>B7*Assumptions!$B$7</f>
         <v>18000</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="28">
         <f t="shared" si="1"/>
-        <v>18000</v>
-      </c>
-      <c r="E49" s="8" t="str">
+        <v>22500</v>
+      </c>
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="B50" s="22">
+        <v>28692</v>
+      </c>
       <c r="C50" s="8">
         <f>B7*Assumptions!$B$9</f>
         <v>22500</v>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="28">
         <f t="shared" si="1"/>
-        <v>22500</v>
-      </c>
-      <c r="E50" s="8" t="str">
+        <v>28692</v>
+      </c>
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="B51" s="22">
+        <v>5646</v>
+      </c>
       <c r="C51" s="8">
         <f>B7*Assumptions!$B$12</f>
         <v>6000</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="28">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>354</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>118</v>
-      </c>
-      <c r="B52" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="B52" s="22">
+        <v>12848</v>
+      </c>
       <c r="C52" s="8">
         <f>B7*Assumptions!$B$13</f>
         <v>3750</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="28">
         <f t="shared" si="1"/>
-        <v>3750</v>
-      </c>
-      <c r="E52" s="8" t="str">
+        <v>12848</v>
+      </c>
+      <c r="E52" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="B53" s="22">
+        <v>5250</v>
+      </c>
       <c r="C53" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>4500</v>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="28">
         <f t="shared" si="1"/>
-        <v>4500</v>
-      </c>
-      <c r="E53" s="8" t="str">
+        <v>5250</v>
+      </c>
+      <c r="E53" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="23">
-        <f>B42-B22*B25</f>
-        <v>189076.19768477289</v>
-      </c>
-      <c r="C54" s="23">
+      <c r="A54" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="26">
+        <f>SUM(B46:B53)</f>
+        <v>191916</v>
+      </c>
+      <c r="C54" s="26">
         <f>SUM(C46:C53)</f>
-        <v>181118.00400000002</v>
-      </c>
-      <c r="D54" s="23">
+        <v>181256.97200000001</v>
+      </c>
+      <c r="D54" s="26">
         <f>SUM(D46:D53)</f>
-        <v>181118.00400000002</v>
-      </c>
-      <c r="E54" s="23">
+        <v>201796.97200000001</v>
+      </c>
+      <c r="E54" s="26">
         <f t="shared" si="0"/>
-        <v>-7958.1936847728794</v>
+        <v>9880.9720000000088</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="8">
         <f>IFERROR(B54/B7,"")</f>
-        <v>12605.079845651526</v>
+        <v>12794.4</v>
       </c>
       <c r="C55" s="8">
         <f>IFERROR(C54/B7,"")</f>
-        <v>12074.533600000001</v>
+        <v>12083.798133333334</v>
       </c>
       <c r="D55" s="8">
         <f>IFERROR(D54/B7,"")</f>
-        <v>12074.533600000001</v>
+        <v>13453.131466666668</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>124</v>
-      </c>
-      <c r="B56" s="17">
+        <v>125</v>
+      </c>
+      <c r="B56" s="18">
         <f>IFERROR(B54/B42,"")</f>
-        <v>0.34472371134020613</v>
-      </c>
-      <c r="C56" s="17">
+        <v>0.34808363649059743</v>
+      </c>
+      <c r="C56" s="18">
         <f>IFERROR(C54/C42,"")</f>
-        <v>0.33020597553969366</v>
-      </c>
-      <c r="D56" s="17">
+        <v>0.32879327406079217</v>
+      </c>
+      <c r="D56" s="18">
         <f>IF(C38&gt;0,IFERROR(D54/C42,""),"")</f>
-        <v>0.33020597553969366</v>
+        <v>0.36605205519726985</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B57" s="26" t="str">
+      <c r="A57" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="29" t="str">
         <f>IF(ISNUMBER(B54),IF(D54&gt;B54*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
-        <v>OM expenses reasonable</v>
+        <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
+      <c r="A59" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
-      <c r="B60" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C60" s="24" t="s">
+      <c r="A60" s="27"/>
+      <c r="B60" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24" t="s">
+      <c r="C60" s="27" t="s">
         <v>94</v>
       </c>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="23">
+      <c r="A61" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="26">
         <f>B42-B54</f>
-        <v>359410</v>
-      </c>
-      <c r="C61" s="23">
+        <v>359434.25</v>
+      </c>
+      <c r="C61" s="26">
         <f>IF(C38&gt;0,C42-D54,"")</f>
-        <v>367382.07599999994</v>
+        <v>349482.46799999994</v>
+      </c>
+      <c r="F61" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B62" s="17">
+      <c r="A62" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="18">
         <f>IFERROR(B61/B22,"")</f>
-        <v>5.6599999999999998E-2</v>
-      </c>
-      <c r="C62" s="17">
+        <v>5.6603818897637798E-2</v>
+      </c>
+      <c r="C62" s="18">
         <f>IF(C61="","",IFERROR(C61/B22,""))</f>
-        <v>5.7855445039370068E-2</v>
+        <v>5.5036609133858258E-2</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="18">
+        <v>132</v>
+      </c>
+      <c r="B63" s="19">
         <f>IFERROR(B22/B38,"")</f>
-        <v>11.23</v>
-      </c>
-      <c r="C63" s="18">
+        <v>11.228504486981123</v>
+      </c>
+      <c r="C63" s="19">
         <f>IF(C38&gt;0,IFERROR(B22/C38,""),"")</f>
-        <v>11.229715773241091</v>
+        <v>11.229954089825485</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B64" s="8">
         <f>IFERROR(B61/B7,"")</f>
-        <v>23960.666666666668</v>
+        <v>23962.283333333333</v>
       </c>
       <c r="C64" s="8">
         <f>IF(C61="","",IFERROR(C61/B7,""))</f>
-        <v>24492.138399999996</v>
+        <v>23298.831199999997</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
+      <c r="A66" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B67" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
@@ -2127,79 +2174,78 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B68" s="8">
         <f>IF(C61="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C61/Assumptions!$B$21/12),""))</f>
-        <v>3977822.6729801958</v>
+        <v>3784014.9964732514</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="21" t="s">
-        <v>135</v>
+      <c r="A69" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="B69" s="8">
         <f>IFERROR(MIN(B67,B68),"")</f>
-        <v>3810000</v>
+        <v>3784014.9964732514</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B70" s="8">
         <f>IFERROR(B22-B69,"")</f>
-        <v>2540000</v>
+        <v>2565985.0035267486</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B71" s="8">
         <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B69)*12,"")</f>
-        <v>281505.90403494623</v>
+        <v>279585.97439999902</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>138</v>
-      </c>
-      <c r="B72" s="18">
+        <v>140</v>
+      </c>
+      <c r="B72" s="19">
         <f>IFERROR(C61/B71,"")</f>
-        <v>1.3050599320801208</v>
+        <v>1.2500000000000042</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B73" s="8">
         <f>IFERROR(C61-B71,"")</f>
-        <v>85876.171965053712</v>
+        <v>69896.493600000918</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>140</v>
-      </c>
-      <c r="B74" s="17">
+        <v>142</v>
+      </c>
+      <c r="B74" s="18">
         <f>IFERROR(B73/B70,"")</f>
-        <v>3.3809516521674687E-2</v>
+        <v>2.7239634488874086E-2</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{0D6F256A-05BA-451B-8A13-558461BAA8F5}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{422C53F8-976D-4B90-A925-C4CCD4F353CF}"/>
   </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup scale="50" orientation="landscape" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/files/08-1811-s-bentley-ave.xlsx
+++ b/files/08-1811-s-bentley-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43BAACF-6CB3-4D36-B6BE-4DB8966A65BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3231C191-68DE-456D-96B0-81B4FEC64C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{390B8E41-5716-4EE3-9120-50D818E7815C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EDF2B707-273B-4FA5-9354-3350A5F7182B}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Lyon Stahl / Serhant / Taksa, rent roll 9/1/2026)</t>
   </si>
   <si>
-    <t>NOTE: | OM: Rent roll cross-check OK: 15 unit rents sum to $47,128/mo vs OM $47,127 (rounding); x12 = $565,536 vs OM $565,525 annual (0.002%).; Expense line items sum to $188,808, not the OM's stated total of $191,916 (short $3,108, 1.6%). NOI of $359,435 is computed off the $191,916 total; recomputed on the li | OM: Rent roll cross-check OK: 15 unit rents sum to $47,128/mo vs OM $47,127 (rounding); x12 = $565,536 vs OM $565,525 annual (0.002%).; Expense line items sum to $188,808, not the OM's stated total of $191,916 (short $3,108, 1.6%). NOI of $359,435 is computed off the $191,916 total; recomputed on the li</t>
+    <t>NOTE: | OM: Rent roll cross-check OK: 15 unit rents sum to $47,128/mo vs OM $47,127 (rounding); x12 = $565,536 vs OM $565,525 annual (0.002%).; Expense line items sum to $188,808, not the OM's stated total of $191,916 (short $3,108, 1.6%). NOI of $359,435 is computed off the $191,916 total; recomputed on the li</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -686,7 +686,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D03B9B2-6CEF-41F3-B3C2-2295EDAC5A09}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{542EBF7E-8D4E-4E83-8C3B-C437E9B617E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -997,7 +997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2298BD12-A3E1-49DB-B66B-7A09864FB10A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC467143-0365-4747-B4F1-69805C3A98CC}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1366,7 +1366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7D02FB-B627-4F17-99CE-137E7BBE5DFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0281AAAA-067A-4CEF-BE1C-4DF7B02328D7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2242,7 +2242,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{422C53F8-976D-4B90-A925-C4CCD4F353CF}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{50A2B422-B5CF-49E6-8BE6-4DB2F0B7B7B0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>

--- a/files/08-1811-s-bentley-ave.xlsx
+++ b/files/08-1811-s-bentley-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3231C191-68DE-456D-96B0-81B4FEC64C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F691ECDF-7756-4197-A014-F66C9B14961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EDF2B707-273B-4FA5-9354-3350A5F7182B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{42F1E642-2337-480A-A093-92B3B78A2CE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="145">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>Year built</t>
+  </si>
+  <si>
+    <t>per Filip 9/17/2026 (LoopNet did not publish)</t>
   </si>
   <si>
     <t>Stories</t>
@@ -484,7 +487,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,6 +534,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -621,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -639,21 +650,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,7 +698,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{542EBF7E-8D4E-4E83-8C3B-C437E9B617E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8AB4790-F825-493C-A2DD-FAFC02E9FED2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -997,7 +1009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC467143-0365-4747-B4F1-69805C3A98CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669D4272-E8F0-4D4B-A02A-ECC940FF2C00}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1366,7 +1378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0281AAAA-067A-4CEF-BE1C-4DF7B02328D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277CDC41-301A-466A-96A7-C64EDCF97A7D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1445,42 +1457,48 @@
       <c r="A11" t="s">
         <v>57</v>
       </c>
+      <c r="B11">
+        <v>1964</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="8">
         <v>5866611</v>
@@ -1488,38 +1506,38 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="4">
         <v>6350000</v>
@@ -1527,7 +1545,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="8">
         <f>IFERROR(B22/B7,"")</f>
@@ -1536,32 +1554,32 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="17">
+        <v>77</v>
+      </c>
+      <c r="B24" s="18">
         <f>IFERROR(B22/B8,"")</f>
         <v>383.26895219700629</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="18">
+        <v>78</v>
+      </c>
+      <c r="B25" s="19">
         <v>5.6599999999999998E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="19">
+        <v>79</v>
+      </c>
+      <c r="B26" s="20">
         <v>11.23</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1570,137 +1588,137 @@
       <c r="F28" s="14"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="B29" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="C29" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="D29" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>85</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B30" s="15">
         <v>1</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="22">
         <v>2900</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="23">
         <f>B30*C30</f>
         <v>2900</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="23">
         <f>D30*12</f>
         <v>34800</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>87</v>
+      <c r="F30" s="24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B31" s="15">
         <v>1</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="22">
         <v>2648</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <f>B31*C31</f>
         <v>2648</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <f>D31*12</f>
         <v>31776</v>
       </c>
-      <c r="F31" s="23" t="s">
-        <v>87</v>
+      <c r="F31" s="24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B32" s="15">
         <v>7</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="22">
         <v>2699</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <f>B32*C32</f>
         <v>18893</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="23">
         <f>D32*12</f>
         <v>226716</v>
       </c>
-      <c r="F32" s="23" t="s">
-        <v>87</v>
+      <c r="F32" s="24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" s="15">
         <v>6</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="22">
         <v>3780</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="23">
         <f>B33*C33</f>
         <v>22680</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="23">
         <f>D33*12</f>
         <v>272160</v>
       </c>
-      <c r="F33" s="23" t="s">
-        <v>87</v>
+      <c r="F33" s="24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="25">
+      <c r="A34" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="26">
         <f>SUM(B30:B33)</f>
         <v>15</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>IFERROR(D34/B34,"")</f>
         <v>3141.4</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <f>SUM(D30:D33)</f>
         <v>47121</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="27">
         <f>SUM(E30:E33)</f>
         <v>565452</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1709,24 +1727,24 @@
       <c r="F36" s="14"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="27" t="s">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27" t="s">
+      <c r="C37" s="28" t="s">
         <v>95</v>
+      </c>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="22">
+        <v>97</v>
+      </c>
+      <c r="B38" s="23">
         <v>565525</v>
       </c>
       <c r="C38" s="8">
@@ -1734,12 +1752,12 @@
         <v>565452</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" s="8">
         <v>2791</v>
@@ -1749,8 +1767,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
-        <v>99</v>
+      <c r="A40" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="B40" s="8">
         <f>B38+B39</f>
@@ -1763,7 +1781,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B41" s="8">
         <f>-B38*0.03</f>
@@ -1774,25 +1792,25 @@
         <v>-16963.559999999998</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B42" s="26">
+      <c r="A42" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="27">
         <f>B40+B41</f>
         <v>551350.25</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <f>C40+C41</f>
         <v>551279.43999999994</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -1801,37 +1819,37 @@
       <c r="F44" s="14"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="27" t="s">
+      <c r="A45" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="B45" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="C45" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="D45" s="28" t="s">
         <v>95</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>107</v>
-      </c>
-      <c r="B46" s="22">
+        <v>108</v>
+      </c>
+      <c r="B46" s="23">
         <v>75399</v>
       </c>
       <c r="C46" s="8">
         <f>B22*Assumptions!$B$15</f>
         <v>79375</v>
       </c>
-      <c r="D46" s="28">
+      <c r="D46" s="29">
         <f>C46</f>
         <v>79375</v>
       </c>
@@ -1840,21 +1858,21 @@
         <v>3976</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B47" s="22">
+        <v>110</v>
+      </c>
+      <c r="B47" s="23">
         <v>19527</v>
       </c>
       <c r="C47" s="8">
         <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
         <v>19568</v>
       </c>
-      <c r="D47" s="28">
+      <c r="D47" s="29">
         <f t="shared" ref="D47:D53" si="1">IF(ISNUMBER(B47),MAX(B47,C47),C47)</f>
         <v>19568</v>
       </c>
@@ -1863,21 +1881,21 @@
         <v>41</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>111</v>
-      </c>
-      <c r="B48" s="22">
+        <v>112</v>
+      </c>
+      <c r="B48" s="23">
         <v>22054</v>
       </c>
       <c r="C48" s="8">
         <f>C42*Assumptions!$B$4</f>
         <v>27563.971999999998</v>
       </c>
-      <c r="D48" s="28">
+      <c r="D48" s="29">
         <f t="shared" si="1"/>
         <v>27563.971999999998</v>
       </c>
@@ -1886,21 +1904,21 @@
         <v>5509.9719999999979</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>113</v>
-      </c>
-      <c r="B49" s="22">
+        <v>114</v>
+      </c>
+      <c r="B49" s="23">
         <v>22500</v>
       </c>
       <c r="C49" s="8">
         <f>B7*Assumptions!$B$7</f>
         <v>18000</v>
       </c>
-      <c r="D49" s="28">
+      <c r="D49" s="29">
         <f t="shared" si="1"/>
         <v>22500</v>
       </c>
@@ -1909,21 +1927,21 @@
         <v>0</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" s="22">
+        <v>116</v>
+      </c>
+      <c r="B50" s="23">
         <v>28692</v>
       </c>
       <c r="C50" s="8">
         <f>B7*Assumptions!$B$9</f>
         <v>22500</v>
       </c>
-      <c r="D50" s="28">
+      <c r="D50" s="29">
         <f t="shared" si="1"/>
         <v>28692</v>
       </c>
@@ -1932,21 +1950,21 @@
         <v>0</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>117</v>
-      </c>
-      <c r="B51" s="22">
+        <v>118</v>
+      </c>
+      <c r="B51" s="23">
         <v>5646</v>
       </c>
       <c r="C51" s="8">
         <f>B7*Assumptions!$B$12</f>
         <v>6000</v>
       </c>
-      <c r="D51" s="28">
+      <c r="D51" s="29">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
@@ -1955,21 +1973,21 @@
         <v>354</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="22">
+        <v>120</v>
+      </c>
+      <c r="B52" s="23">
         <v>12848</v>
       </c>
       <c r="C52" s="8">
         <f>B7*Assumptions!$B$13</f>
         <v>3750</v>
       </c>
-      <c r="D52" s="28">
+      <c r="D52" s="29">
         <f t="shared" si="1"/>
         <v>12848</v>
       </c>
@@ -1978,21 +1996,21 @@
         <v>0</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>121</v>
-      </c>
-      <c r="B53" s="22">
+        <v>122</v>
+      </c>
+      <c r="B53" s="23">
         <v>5250</v>
       </c>
       <c r="C53" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>4500</v>
       </c>
-      <c r="D53" s="28">
+      <c r="D53" s="29">
         <f t="shared" si="1"/>
         <v>5250</v>
       </c>
@@ -2001,36 +2019,36 @@
         <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="26">
+      <c r="A54" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="27">
         <f>SUM(B46:B53)</f>
         <v>191916</v>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="27">
         <f>SUM(C46:C53)</f>
         <v>181256.97200000001</v>
       </c>
-      <c r="D54" s="26">
+      <c r="D54" s="27">
         <f>SUM(D46:D53)</f>
         <v>201796.97200000001</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="27">
         <f t="shared" si="0"/>
         <v>9880.9720000000088</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="8">
         <f>IFERROR(B54/B7,"")</f>
@@ -2047,33 +2065,33 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="18">
+        <v>126</v>
+      </c>
+      <c r="B56" s="19">
         <f>IFERROR(B54/B42,"")</f>
         <v>0.34808363649059743</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="19">
         <f>IFERROR(C54/C42,"")</f>
         <v>0.32879327406079217</v>
       </c>
-      <c r="D56" s="18">
+      <c r="D56" s="19">
         <f>IF(C38&gt;0,IFERROR(D54/C42,""),"")</f>
         <v>0.36605205519726985</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="29" t="str">
+      <c r="A57" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="30" t="str">
         <f>IF(ISNUMBER(B54),IF(D54&gt;B54*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
         <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2082,67 +2100,67 @@
       <c r="F59" s="14"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
-      <c r="B60" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" s="27" t="s">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27" t="s">
+      <c r="C60" s="28" t="s">
         <v>95</v>
       </c>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B61" s="26">
+      <c r="A61" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="27">
         <f>B42-B54</f>
         <v>359434.25</v>
       </c>
-      <c r="C61" s="26">
+      <c r="C61" s="27">
         <f>IF(C38&gt;0,C42-D54,"")</f>
         <v>349482.46799999994</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="B62" s="18">
+      <c r="A62" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="19">
         <f>IFERROR(B61/B22,"")</f>
         <v>5.6603818897637798E-2</v>
       </c>
-      <c r="C62" s="18">
+      <c r="C62" s="19">
         <f>IF(C61="","",IFERROR(C61/B22,""))</f>
         <v>5.5036609133858258E-2</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>132</v>
-      </c>
-      <c r="B63" s="19">
+        <v>133</v>
+      </c>
+      <c r="B63" s="20">
         <f>IFERROR(B22/B38,"")</f>
         <v>11.228504486981123</v>
       </c>
-      <c r="C63" s="19">
+      <c r="C63" s="20">
         <f>IF(C38&gt;0,IFERROR(B22/C38,""),"")</f>
         <v>11.229954089825485</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B64" s="8">
         <f>IFERROR(B61/B7,"")</f>
@@ -2155,7 +2173,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2165,7 +2183,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B67" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
@@ -2174,7 +2192,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B68" s="8">
         <f>IF(C61="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C61/Assumptions!$B$21/12),""))</f>
@@ -2182,8 +2200,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="24" t="s">
-        <v>137</v>
+      <c r="A69" s="25" t="s">
+        <v>138</v>
       </c>
       <c r="B69" s="8">
         <f>IFERROR(MIN(B67,B68),"")</f>
@@ -2192,7 +2210,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B70" s="8">
         <f>IFERROR(B22-B69,"")</f>
@@ -2201,7 +2219,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B71" s="8">
         <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B69)*12,"")</f>
@@ -2210,16 +2228,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>140</v>
-      </c>
-      <c r="B72" s="19">
+        <v>141</v>
+      </c>
+      <c r="B72" s="20">
         <f>IFERROR(C61/B71,"")</f>
         <v>1.2500000000000042</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B73" s="8">
         <f>IFERROR(C61-B71,"")</f>
@@ -2228,21 +2246,21 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>142</v>
-      </c>
-      <c r="B74" s="18">
+        <v>143</v>
+      </c>
+      <c r="B74" s="19">
         <f>IFERROR(B73/B70,"")</f>
         <v>2.7239634488874086E-2</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{50A2B422-B5CF-49E6-8BE6-4DB2F0B7B7B0}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{473D3D7F-B4C1-4234-A58D-59FE728B1101}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>
